--- a/artfynd/A 41282-2024 artfynd.xlsx
+++ b/artfynd/A 41282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121156577</v>
+        <v>121094538</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>74708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510584</v>
+        <v>510497</v>
       </c>
       <c r="R2" t="n">
-        <v>7002017</v>
+        <v>7002070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,6 +769,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,7 +794,7 @@
         <v>121094426</v>
       </c>
       <c r="B3" t="n">
-        <v>78335</v>
+        <v>78338</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -922,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121094538</v>
+        <v>121094927</v>
       </c>
       <c r="B4" t="n">
-        <v>74705</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510497</v>
+        <v>510420</v>
       </c>
       <c r="R4" t="n">
-        <v>7002070</v>
+        <v>7002092</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1025,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>På frisk- och frisk-fuktig mark.</t>
+          <t>På frisk mark. Tidigare brandpåverkad.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1038,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121094655</v>
+        <v>121156577</v>
       </c>
       <c r="B5" t="n">
-        <v>78335</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,25 +1055,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,14 +1082,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510467</v>
+        <v>510584</v>
       </c>
       <c r="R5" t="n">
-        <v>7002097</v>
+        <v>7002017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,26 +1137,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1169,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121094927</v>
+        <v>121094655</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>78338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,25 +1166,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1212,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510420</v>
+        <v>510467</v>
       </c>
       <c r="R6" t="n">
-        <v>7002092</v>
+        <v>7002097</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,9 +1250,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>På frisk mark. Tidigare brandpåverkad.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 41282-2024 artfynd.xlsx
+++ b/artfynd/A 41282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121094538</v>
+        <v>121156577</v>
       </c>
       <c r="B2" t="n">
-        <v>74708</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510497</v>
+        <v>510584</v>
       </c>
       <c r="R2" t="n">
-        <v>7002070</v>
+        <v>7002017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,11 +769,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121094426</v>
+        <v>121094655</v>
       </c>
       <c r="B3" t="n">
         <v>78338</v>
@@ -834,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510497</v>
+        <v>510467</v>
       </c>
       <c r="R3" t="n">
-        <v>7002070</v>
+        <v>7002097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,11 +882,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>På frisk mark.</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>tall</t>
@@ -909,7 +899,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
+          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121094927</v>
+        <v>121094426</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>78338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -970,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510420</v>
+        <v>510497</v>
       </c>
       <c r="R4" t="n">
-        <v>7002092</v>
+        <v>7002070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1015,27 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>På frisk mark. Tidigare brandpåverkad.</t>
+          <t>På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1043,7 +1053,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121156577</v>
+        <v>121094927</v>
       </c>
       <c r="B5" t="n">
         <v>91973</v>
@@ -1082,14 +1092,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510584</v>
+        <v>510420</v>
       </c>
       <c r="R5" t="n">
-        <v>7002017</v>
+        <v>7002092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,6 +1147,11 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>På frisk mark. Tidigare brandpåverkad.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1154,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121094655</v>
+        <v>121094538</v>
       </c>
       <c r="B6" t="n">
-        <v>78338</v>
+        <v>74708</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,21 +1185,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1197,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510467</v>
+        <v>510497</v>
       </c>
       <c r="R6" t="n">
-        <v>7002097</v>
+        <v>7002070</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,24 +1265,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 41282-2024 artfynd.xlsx
+++ b/artfynd/A 41282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121156577</v>
+        <v>121094927</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510584</v>
+        <v>510420</v>
       </c>
       <c r="R2" t="n">
-        <v>7002017</v>
+        <v>7002092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,6 +769,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>På frisk mark. Tidigare brandpåverkad.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121094655</v>
+        <v>121094426</v>
       </c>
       <c r="B3" t="n">
-        <v>78338</v>
+        <v>78341</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510467</v>
+        <v>510497</v>
       </c>
       <c r="R3" t="n">
-        <v>7002097</v>
+        <v>7002070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +887,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>På frisk mark.</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>tall</t>
@@ -899,7 +909,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
+          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121094426</v>
+        <v>121094655</v>
       </c>
       <c r="B4" t="n">
-        <v>78338</v>
+        <v>78341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510497</v>
+        <v>510467</v>
       </c>
       <c r="R4" t="n">
-        <v>7002070</v>
+        <v>7002097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,11 +1023,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>På frisk mark.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>tall</t>
@@ -1035,7 +1040,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
+          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121094927</v>
+        <v>121094538</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>74710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1096,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510420</v>
+        <v>510497</v>
       </c>
       <c r="R5" t="n">
-        <v>7002092</v>
+        <v>7002070</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,7 +1156,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>På frisk mark. Tidigare brandpåverkad.</t>
+          <t>På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1169,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121094538</v>
+        <v>121156577</v>
       </c>
       <c r="B6" t="n">
-        <v>74708</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,25 +1186,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1208,14 +1213,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510497</v>
+        <v>510584</v>
       </c>
       <c r="R6" t="n">
-        <v>7002070</v>
+        <v>7002017</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,11 +1268,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 41282-2024 artfynd.xlsx
+++ b/artfynd/A 41282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121094927</v>
+        <v>121156577</v>
       </c>
       <c r="B2" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510420</v>
+        <v>510584</v>
       </c>
       <c r="R2" t="n">
-        <v>7002092</v>
+        <v>7002017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,11 +769,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>På frisk mark. Tidigare brandpåverkad.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121094426</v>
+        <v>121094538</v>
       </c>
       <c r="B3" t="n">
-        <v>78341</v>
+        <v>74710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,27 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>På frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
+          <t>På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121094655</v>
+        <v>121094426</v>
       </c>
       <c r="B4" t="n">
         <v>78341</v>
@@ -970,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510467</v>
+        <v>510497</v>
       </c>
       <c r="R4" t="n">
-        <v>7002097</v>
+        <v>7002070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,6 +998,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>På frisk mark.</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>tall</t>
@@ -1040,7 +1020,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
+          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1058,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121094538</v>
+        <v>121094655</v>
       </c>
       <c r="B5" t="n">
-        <v>74710</v>
+        <v>78341</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,21 +1054,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1101,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510497</v>
+        <v>510467</v>
       </c>
       <c r="R5" t="n">
-        <v>7002070</v>
+        <v>7002097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,9 +1134,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>På frisk- och frisk-fuktig mark.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1174,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121156577</v>
+        <v>121094927</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,14 +1208,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510584</v>
+        <v>510420</v>
       </c>
       <c r="R6" t="n">
-        <v>7002017</v>
+        <v>7002092</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,6 +1263,11 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>På frisk mark. Tidigare brandpåverkad.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 41282-2024 artfynd.xlsx
+++ b/artfynd/A 41282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121156577</v>
+        <v>121094538</v>
       </c>
       <c r="B2" t="n">
-        <v>91986</v>
+        <v>74713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510584</v>
+        <v>510497</v>
       </c>
       <c r="R2" t="n">
-        <v>7002017</v>
+        <v>7002070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,6 +769,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121094538</v>
+        <v>121094927</v>
       </c>
       <c r="B3" t="n">
-        <v>74710</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510497</v>
+        <v>510420</v>
       </c>
       <c r="R3" t="n">
-        <v>7002070</v>
+        <v>7002092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>På frisk- och frisk-fuktig mark.</t>
+          <t>På frisk mark. Tidigare brandpåverkad.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121094426</v>
+        <v>121094655</v>
       </c>
       <c r="B4" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510497</v>
+        <v>510467</v>
       </c>
       <c r="R4" t="n">
-        <v>7002070</v>
+        <v>7002097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,11 +1003,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>På frisk mark.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>tall</t>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
+          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121094655</v>
+        <v>121094426</v>
       </c>
       <c r="B5" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510467</v>
+        <v>510497</v>
       </c>
       <c r="R5" t="n">
-        <v>7002097</v>
+        <v>7002070</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,6 +1134,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>På frisk mark.</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>tall</t>
@@ -1151,7 +1156,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
+          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1169,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121094927</v>
+        <v>121156577</v>
       </c>
       <c r="B6" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,14 +1213,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510420</v>
+        <v>510584</v>
       </c>
       <c r="R6" t="n">
-        <v>7002092</v>
+        <v>7002017</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,11 +1268,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>På frisk mark. Tidigare brandpåverkad.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 41282-2024 artfynd.xlsx
+++ b/artfynd/A 41282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121094538</v>
+        <v>121094655</v>
       </c>
       <c r="B2" t="n">
-        <v>74713</v>
+        <v>78344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510497</v>
+        <v>510467</v>
       </c>
       <c r="R2" t="n">
-        <v>7002070</v>
+        <v>7002097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,9 +771,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>På frisk- och frisk-fuktig mark.</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121094927</v>
+        <v>121094426</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>78344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +818,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510420</v>
+        <v>510497</v>
       </c>
       <c r="R3" t="n">
-        <v>7002092</v>
+        <v>7002070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +904,27 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>På frisk mark. Tidigare brandpåverkad.</t>
+          <t>På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121094655</v>
+        <v>121094538</v>
       </c>
       <c r="B4" t="n">
-        <v>78344</v>
+        <v>74713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +958,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510467</v>
+        <v>510497</v>
       </c>
       <c r="R4" t="n">
-        <v>7002097</v>
+        <v>7002070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,24 +1038,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1038,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121094426</v>
+        <v>121156577</v>
       </c>
       <c r="B5" t="n">
-        <v>78344</v>
+        <v>91989</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,14 +1097,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510497</v>
+        <v>510584</v>
       </c>
       <c r="R5" t="n">
-        <v>7002070</v>
+        <v>7002017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,31 +1152,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>På frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Fire killed tree # En kolad stubbe. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1174,7 +1169,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121156577</v>
+        <v>121094927</v>
       </c>
       <c r="B6" t="n">
         <v>91989</v>
@@ -1213,14 +1208,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råkmyren, Kullen, Brunflo, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510584</v>
+        <v>510420</v>
       </c>
       <c r="R6" t="n">
-        <v>7002017</v>
+        <v>7002092</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,6 +1263,11 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>På frisk mark. Tidigare brandpåverkad.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
